--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-08-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-08-2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922D9191-6AE4-4029-B900-F224DAA9886D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D351C245-73F0-4306-AAF3-38FC702AF6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng tính CK" sheetId="1" r:id="rId1"/>
@@ -816,6 +816,21 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -864,19 +879,67 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -888,75 +951,74 @@
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="7"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -966,73 +1028,11 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1519,74 +1519,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="80"/>
-      <c r="B1" s="81"/>
-      <c r="C1" s="88" t="s">
+      <c r="A1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="85" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="87"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="93" t="s">
+      <c r="A3" s="85"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="95"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="100"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="82" t="s">
+      <c r="A4" s="85"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="84"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="89"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="96" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="92"/>
-      <c r="D5" s="92"/>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="43"/>
       <c r="C6" s="43"/>
       <c r="D6" s="44"/>
-      <c r="E6" s="90" t="str">
+      <c r="E6" s="95" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 28 tháng 08 năm 2026</v>
       </c>
-      <c r="F6" s="90"/>
+      <c r="F6" s="95"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="89"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
       <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1685,10 +1685,10 @@
       <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="96" t="s">
+      <c r="A14" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="97"/>
+      <c r="B14" s="81"/>
       <c r="C14" s="28">
         <f>SUM(C11:C13)</f>
         <v>395</v>
@@ -1698,12 +1698,12 @@
       <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="98"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
       <c r="E15" s="27">
         <f>SUM(E11:E13)</f>
         <v>2648000</v>
@@ -1727,33 +1727,33 @@
       <c r="F17" s="18"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="99"/>
+      <c r="B18" s="83"/>
       <c r="C18" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="99" t="s">
+      <c r="D18" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="99"/>
+      <c r="E18" s="83"/>
       <c r="F18" s="62" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="100" t="s">
+      <c r="A19" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="100"/>
+      <c r="B19" s="84"/>
       <c r="C19" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="100" t="s">
+      <c r="D19" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="100"/>
+      <c r="E19" s="84"/>
       <c r="F19" s="17" t="s">
         <v>7</v>
       </c>
@@ -1791,17 +1791,17 @@
       <c r="F23" s="41"/>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="99" t="s">
+      <c r="A24" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="99"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="99" t="s">
+      <c r="D24" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="99"/>
+      <c r="E24" s="83"/>
       <c r="F24" s="62" t="s">
         <v>9</v>
       </c>
@@ -1840,6 +1840,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A18:B18"/>
@@ -1848,14 +1856,6 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="C3:F3"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1888,64 +1888,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="111"/>
-      <c r="B1" s="112"/>
-      <c r="C1" s="113" t="s">
+      <c r="A1" s="108"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="110" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="111"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="122" t="s">
+      <c r="A2" s="108"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="119" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="124"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="121"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="111"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="93" t="s">
+      <c r="A3" s="108"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="95"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="100"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="111"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="82" t="s">
+      <c r="A4" s="108"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="84"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="89"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="115"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="117"/>
+      <c r="B5" s="112"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="114"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="48"/>
@@ -1994,10 +1994,10 @@
       <c r="H9" s="35"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="118" t="s">
+      <c r="A10" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="119"/>
+      <c r="B10" s="116"/>
       <c r="C10" s="26">
         <f>'Bảng tính CK'!E15</f>
         <v>2648000</v>
@@ -2009,10 +2009,10 @@
       <c r="H10" s="35"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="104" t="s">
+      <c r="A11" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="105"/>
+      <c r="B11" s="102"/>
       <c r="C11" s="26">
         <v>3</v>
       </c>
@@ -2023,10 +2023,10 @@
       <c r="H11" s="35"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="120" t="s">
+      <c r="A12" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="121"/>
+      <c r="B12" s="118"/>
       <c r="C12" s="24">
         <v>0</v>
       </c>
@@ -2037,10 +2037,10 @@
       <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="109" t="s">
+      <c r="A13" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="110"/>
+      <c r="B13" s="107"/>
       <c r="C13" s="24">
         <f>COUNTIFS(C16:C20, "&gt;=2.5",C16:C20,"&lt;7")</f>
         <v>0</v>
@@ -2172,11 +2172,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="106" t="s">
+      <c r="A19" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="107"/>
-      <c r="C19" s="108"/>
+      <c r="B19" s="104"/>
+      <c r="C19" s="105"/>
       <c r="D19" s="58">
         <f>SUM(D16:D18)</f>
         <v>3</v>
@@ -2209,11 +2209,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="96" t="s">
+      <c r="A21" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="101"/>
-      <c r="C21" s="97"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="81"/>
       <c r="D21" s="19"/>
       <c r="E21" s="27">
         <f>SUM(E16:E18)</f>
@@ -2256,40 +2256,40 @@
       <c r="H23" s="35"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="99" t="s">
+      <c r="A24" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="99"/>
-      <c r="C24" s="99" t="s">
+      <c r="B24" s="83"/>
+      <c r="C24" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="99"/>
-      <c r="E24" s="102" t="s">
+      <c r="D24" s="83"/>
+      <c r="E24" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="102"/>
-      <c r="G24" s="99" t="s">
+      <c r="F24" s="123"/>
+      <c r="G24" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="99"/>
+      <c r="H24" s="83"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="100" t="s">
+      <c r="A25" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="100"/>
-      <c r="C25" s="100" t="s">
+      <c r="B25" s="84"/>
+      <c r="C25" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="100"/>
-      <c r="E25" s="103" t="s">
+      <c r="D25" s="84"/>
+      <c r="E25" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="103"/>
-      <c r="G25" s="100" t="s">
+      <c r="F25" s="124"/>
+      <c r="G25" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="100"/>
+      <c r="H25" s="84"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="34"/>
@@ -2332,36 +2332,25 @@
       <c r="H29" s="35"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="99" t="s">
+      <c r="A30" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="99"/>
-      <c r="C30" s="99" t="s">
+      <c r="B30" s="83"/>
+      <c r="C30" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="99"/>
-      <c r="E30" s="102" t="s">
+      <c r="D30" s="83"/>
+      <c r="E30" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="102"/>
-      <c r="G30" s="99" t="s">
+      <c r="F30" s="123"/>
+      <c r="G30" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="99"/>
+      <c r="H30" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A30:B30"/>
@@ -2375,6 +2364,17 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
@@ -2404,55 +2404,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="139"/>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="140" t="s">
+      <c r="A1" s="134"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="135" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="146" t="s">
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="147"/>
+      <c r="H1" s="142"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="139"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="146" t="s">
+      <c r="A2" s="134"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="141" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="147"/>
+      <c r="H2" s="142"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="139"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="145"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="146" t="s">
+      <c r="A3" s="134"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="147"/>
+      <c r="H3" s="142"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="138" t="str">
+      <c r="A4" s="133" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 28 tháng 08 năm 2026</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
+      <c r="B4" s="133"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="133"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
@@ -2489,27 +2489,27 @@
       <c r="H7" s="69"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="148" t="s">
+      <c r="A8" s="127" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="148" t="s">
+      <c r="B8" s="127" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="150" t="s">
+      <c r="C8" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="151"/>
-      <c r="E8" s="151"/>
-      <c r="F8" s="152"/>
-      <c r="G8" s="153" t="s">
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="153"/>
+      <c r="H8" s="132"/>
       <c r="I8" s="33"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="149"/>
-      <c r="B9" s="149"/>
+      <c r="A9" s="128"/>
+      <c r="B9" s="128"/>
       <c r="C9" s="74" t="s">
         <v>60</v>
       </c>
@@ -2522,8 +2522,8 @@
       <c r="F9" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="153"/>
-      <c r="H9" s="153"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
       <c r="I9" s="33"/>
     </row>
     <row r="10" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2624,10 +2624,10 @@
         <f>D13-E13</f>
         <v>2</v>
       </c>
-      <c r="G13" s="130" t="s">
+      <c r="G13" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="130"/>
+      <c r="H13" s="146"/>
       <c r="I13" s="33"/>
     </row>
     <row r="14" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2650,10 +2650,10 @@
         <f t="shared" ref="F14" si="0">D14</f>
         <v>178</v>
       </c>
-      <c r="G14" s="130" t="s">
+      <c r="G14" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="130"/>
+      <c r="H14" s="146"/>
       <c r="I14" s="33"/>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2676,10 +2676,10 @@
         <f>D15-E15</f>
         <v>52</v>
       </c>
-      <c r="G15" s="130" t="s">
+      <c r="G15" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="130"/>
+      <c r="H15" s="146"/>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="55">
@@ -2701,10 +2701,10 @@
         <f>D16-E16</f>
         <v>22</v>
       </c>
-      <c r="G16" s="130" t="s">
+      <c r="G16" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="130"/>
+      <c r="H16" s="146"/>
     </row>
     <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55">
@@ -2726,10 +2726,10 @@
         <f>D17-E17</f>
         <v>2</v>
       </c>
-      <c r="G17" s="130" t="s">
+      <c r="G17" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="130"/>
+      <c r="H17" s="146"/>
     </row>
     <row r="18" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="55">
@@ -2750,10 +2750,10 @@
       <c r="F18" s="23">
         <v>3</v>
       </c>
-      <c r="G18" s="130" t="s">
+      <c r="G18" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="130"/>
+      <c r="H18" s="146"/>
     </row>
     <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="55">
@@ -2773,10 +2773,10 @@
         <f>SUM(D19-E19)</f>
         <v>2</v>
       </c>
-      <c r="G19" s="136" t="s">
+      <c r="G19" s="147" t="s">
         <v>68</v>
       </c>
-      <c r="H19" s="137"/>
+      <c r="H19" s="148"/>
     </row>
     <row r="20" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="55">
@@ -2798,16 +2798,16 @@
         <f>SUM(D20-E20)</f>
         <v>1</v>
       </c>
-      <c r="G20" s="135" t="s">
+      <c r="G20" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="H20" s="135"/>
+      <c r="H20" s="145"/>
     </row>
     <row r="21" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="131" t="s">
+      <c r="A21" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="132"/>
+      <c r="B21" s="153"/>
       <c r="C21" s="56">
         <f>SUM(C10:C20)</f>
         <v>6460</v>
@@ -2824,8 +2824,8 @@
         <f>SUM(F10:F20)</f>
         <v>3011</v>
       </c>
-      <c r="G21" s="133"/>
-      <c r="H21" s="134"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="144"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="69"/>
@@ -2838,40 +2838,40 @@
       <c r="H22" s="69"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="129" t="s">
+      <c r="A23" s="151" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="129"/>
-      <c r="C23" s="129" t="s">
+      <c r="B23" s="151"/>
+      <c r="C23" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="129"/>
-      <c r="E23" s="129" t="s">
+      <c r="D23" s="151"/>
+      <c r="E23" s="151" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="129"/>
-      <c r="G23" s="99" t="s">
+      <c r="F23" s="151"/>
+      <c r="G23" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="99"/>
+      <c r="H23" s="83"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="128" t="s">
+      <c r="A24" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="128"/>
-      <c r="C24" s="128" t="s">
+      <c r="B24" s="150"/>
+      <c r="C24" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128" t="s">
+      <c r="D24" s="150"/>
+      <c r="E24" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="128"/>
-      <c r="G24" s="128" t="s">
+      <c r="F24" s="150"/>
+      <c r="G24" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="128"/>
+      <c r="H24" s="150"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="75"/>
@@ -2914,22 +2914,22 @@
       <c r="H28" s="77"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="127" t="s">
+      <c r="A29" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="127"/>
-      <c r="C29" s="127" t="s">
+      <c r="B29" s="149"/>
+      <c r="C29" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="127"/>
-      <c r="E29" s="127" t="s">
+      <c r="D29" s="149"/>
+      <c r="E29" s="149" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="127"/>
-      <c r="G29" s="127" t="s">
+      <c r="F29" s="149"/>
+      <c r="G29" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="H29" s="127"/>
+      <c r="H29" s="149"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="69"/>
@@ -2943,25 +2943,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H9"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A29:B29"/>
@@ -2978,6 +2959,25 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
